--- a/config/default/forms/contact/person-create.xlsx
+++ b/config/default/forms/contact/person-create.xlsx
@@ -1,22 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="0"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\apoorva\cht-core\config\default\forms\contact\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD340967-00E9-4B5B-8D31-2F37A1FC616D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="survey" sheetId="1" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="330">
   <si>
     <t>type</t>
   </si>
@@ -111,7 +128,7 @@
     <t>default</t>
   </si>
   <si>
-    <t xml:space="preserve">begin group</t>
+    <t>begin group</t>
   </si>
   <si>
     <t>inputs</t>
@@ -132,10 +149,10 @@
     <t>contact_id</t>
   </si>
   <si>
-    <t xml:space="preserve">Contact ID of the logged in user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Namba ya Usajilisho ya mtumiaji wa huduma hii</t>
+    <t>Contact ID of the logged in user</t>
+  </si>
+  <si>
+    <t>Namba ya Usajilisho ya mtumiaji wa huduma hii</t>
   </si>
   <si>
     <r>
@@ -156,13 +173,13 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Identifiant du contact</t>
+    <t>Identifiant du contact</t>
   </si>
   <si>
     <t>facility_id</t>
   </si>
   <si>
-    <t xml:space="preserve">Place ID of the logged in user</t>
+    <t>Place ID of the logged in user</t>
   </si>
   <si>
     <r>
@@ -183,10 +200,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">ID Tempat dari login user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitambulisho cha mahali cha mtumizi wa huduma hii</t>
+    <t>ID Tempat dari login user</t>
+  </si>
+  <si>
+    <t>Kitambulisho cha mahali cha mtumizi wa huduma hii</t>
   </si>
   <si>
     <r>
@@ -207,58 +224,55 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Identifiant du centre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name of the logged in user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">लॉग इन यूज़र का नाम</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nama dari login user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jina ya mtumizi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">लग इन गरेको प्रयोगकर्ताको नाम</t>
+    <t>Identifiant du centre</t>
+  </si>
+  <si>
+    <t>Name of the logged in user</t>
+  </si>
+  <si>
+    <t>लॉग इन यूज़र का नाम</t>
+  </si>
+  <si>
+    <t>Nama dari login user</t>
+  </si>
+  <si>
+    <t>Jina ya mtumizi</t>
+  </si>
+  <si>
+    <t>लग इन गरेको प्रयोगकर्ताको नाम</t>
   </si>
   <si>
     <t>Nom</t>
   </si>
   <si>
-    <t xml:space="preserve">end group</t>
+    <t>end group</t>
   </si>
   <si>
     <t>init</t>
   </si>
   <si>
-    <t xml:space="preserve">Cannot be inside the person group without having all fields saved to person. And needs separate db-objects because cannot have one that handles the different place types. Last part is now incorrect... as long as it is read only it could be a string of appearance db-object and work fine.</t>
+    <t>Cannot be inside the person group without having all fields saved to person. And needs separate db-objects because cannot have one that handles the different place types. Last part is now incorrect... as long as it is read only it could be a string of appearance db-object and work fine.</t>
   </si>
   <si>
     <t>parent_id</t>
   </si>
   <si>
-    <t xml:space="preserve">Belongs To</t>
-  </si>
-  <si>
-    <t xml:space="preserve">यह व्यक्ति इस जगह से जुड़ा है</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orang ini terhubung ke tempat ini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ni wa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">यो व्यक्ति यस ठाउँसँग सम्बन्धित छ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Associé avec</t>
-  </si>
-  <si>
-    <t>db-object</t>
+    <t>Belongs To</t>
+  </si>
+  <si>
+    <t>यह व्यक्ति इस जगह से जुड़ा है</t>
+  </si>
+  <si>
+    <t>Orang ini terhubung ke tempat ini</t>
+  </si>
+  <si>
+    <t>Ni wa</t>
+  </si>
+  <si>
+    <t>यो व्यक्ति यस ठाउँसँग सम्बन्धित छ</t>
+  </si>
+  <si>
+    <t>Associé avec</t>
   </si>
   <si>
     <t>true</t>
@@ -273,7 +287,7 @@
     <t>hidden</t>
   </si>
   <si>
-    <t xml:space="preserve">select_one place_type</t>
+    <t>select_one place_type</t>
   </si>
   <si>
     <t>type_selector</t>
@@ -297,7 +311,7 @@
     <t>parent</t>
   </si>
   <si>
-    <t xml:space="preserve">Parent ID</t>
+    <t>Parent ID</t>
   </si>
   <si>
     <r>
@@ -318,25 +332,25 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Asli ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID ya mzazi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">identifiant du parent</t>
+    <t>Asli ID</t>
+  </si>
+  <si>
+    <t>ID ya mzazi</t>
+  </si>
+  <si>
+    <t>identifiant du parent</t>
   </si>
   <si>
     <t>PARENT</t>
   </si>
   <si>
-    <t xml:space="preserve">Person Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">व्यक्ति के प्रकार</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipe Orang</t>
+    <t>Person Type</t>
+  </si>
+  <si>
+    <t>व्यक्ति के प्रकार</t>
+  </si>
+  <si>
+    <t>Tipe Orang</t>
   </si>
   <si>
     <t>Jina</t>
@@ -345,7 +359,7 @@
     <t>Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Full name</t>
+    <t>Full name</t>
   </si>
   <si>
     <t>नाम</t>
@@ -363,19 +377,19 @@
     <t>short_name</t>
   </si>
   <si>
-    <t xml:space="preserve">Short name</t>
+    <t>Short name</t>
   </si>
   <si>
     <t>no</t>
   </si>
   <si>
-    <t xml:space="preserve">string-length(.) &lt;= 10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Short name can not be more than 10 characters long.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Please enter a short name that is preferred by the person.</t>
+    <t>string-length(.) &lt;= 10</t>
+  </si>
+  <si>
+    <t>Short name can not be more than 10 characters long.</t>
+  </si>
+  <si>
+    <t>Please enter a short name that is preferred by the person.</t>
   </si>
   <si>
     <t>date_of_birth</t>
@@ -405,13 +419,13 @@
     <t>not(selected(../dob_method,'approx'))</t>
   </si>
   <si>
-    <t xml:space="preserve">. &lt;= now()</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date must be before today</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date of Birth</t>
+    <t>. &lt;= now()</t>
+  </si>
+  <si>
+    <t>Date must be before today</t>
+  </si>
+  <si>
+    <t>Date of Birth</t>
   </si>
   <si>
     <t>note</t>
@@ -420,7 +434,7 @@
     <t>age_label</t>
   </si>
   <si>
-    <t xml:space="preserve">**Please enter date of birth**</t>
+    <t>**Please enter date of birth**</t>
   </si>
   <si>
     <t>selected(../dob_method,'approx')</t>
@@ -435,10 +449,10 @@
     <t>Years</t>
   </si>
   <si>
-    <t xml:space="preserve">. &gt;= 0 and . &lt;= 130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age must be between 0 and 130</t>
+    <t>. &gt;= 0 and . &lt;= 130</t>
+  </si>
+  <si>
+    <t>Age must be between 0 and 130</t>
   </si>
   <si>
     <t>age_months</t>
@@ -447,13 +461,13 @@
     <t>Months</t>
   </si>
   <si>
-    <t xml:space="preserve">. &gt;= 0 and . &lt;= 11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Months must between 0 and 11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">select_multiple select_dob_method</t>
+    <t>. &gt;= 0 and . &lt;= 11</t>
+  </si>
+  <si>
+    <t>Months must between 0 and 11</t>
+  </si>
+  <si>
+    <t>select_multiple select_dob_method</t>
   </si>
   <si>
     <t>dob_method</t>
@@ -468,13 +482,13 @@
     <t>dob_approx</t>
   </si>
   <si>
-    <t xml:space="preserve">add-date(today(), 0-${age_years}, 0-${age_months})</t>
+    <t>add-date(today(), 0-${age_years}, 0-${age_months})</t>
   </si>
   <si>
     <t>dob_raw</t>
   </si>
   <si>
-    <t xml:space="preserve">if(not(selected( ${dob_method},'approx')), 
+    <t>if(not(selected( ${dob_method},'approx')), 
 ${dob_calendar},
 ${dob_approx})</t>
   </si>
@@ -488,12 +502,12 @@
     <t>dob_debug</t>
   </si>
   <si>
-    <t xml:space="preserve">DOB Approx: ${dob_approx}
+    <t>DOB Approx: ${dob_approx}
 DOB Calendar: ${dob_calendar}
 DOB ISO: ${dob_iso}</t>
   </si>
   <si>
-    <t xml:space="preserve">select_one male_female</t>
+    <t>select_one male_female</t>
   </si>
   <si>
     <t>sex</t>
@@ -505,7 +519,7 @@
     <t>लिंग</t>
   </si>
   <si>
-    <t xml:space="preserve">Jenis kelamin</t>
+    <t>Jenis kelamin</t>
   </si>
   <si>
     <t>Jinsia</t>
@@ -520,19 +534,19 @@
     <t>phone</t>
   </si>
   <si>
-    <t xml:space="preserve">Phone Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">फोन नंबर</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nomor Telepon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nambari ya simu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">फोन नम्बर</t>
+    <t>Phone Number</t>
+  </si>
+  <si>
+    <t>फोन नंबर</t>
+  </si>
+  <si>
+    <t>Nomor Telepon</t>
+  </si>
+  <si>
+    <t>Nambari ya simu</t>
+  </si>
+  <si>
+    <t>फोन नम्बर</t>
   </si>
   <si>
     <t>Téléphone</t>
@@ -541,7 +555,7 @@
     <t>true()</t>
   </si>
   <si>
-    <t xml:space="preserve">Please enter a valid local number, or use the standard international format, which includes a plus sign (+) and country code. For example: +254712345678</t>
+    <t>Please enter a valid local number, or use the standard international format, which includes a plus sign (+) and country code. For example: +254712345678</t>
   </si>
   <si>
     <r>
@@ -550,7 +564,7 @@
         <color indexed="64"/>
         <rFont val="Droid Sans Devanagari"/>
       </rPr>
-      <t xml:space="preserve">कृपया एक सही स्थानीय नंबर दर्ज करें</t>
+      <t>कृपया एक सही स्थानीय नंबर दर्ज करें</t>
     </r>
     <r>
       <rPr>
@@ -566,7 +580,7 @@
         <color indexed="64"/>
         <rFont val="Droid Sans Devanagari"/>
       </rPr>
-      <t xml:space="preserve">या मानक अंतरराष्ट्रीय प्रारूप का उपयोग करें</t>
+      <t>या मानक अंतरराष्ट्रीय प्रारूप का उपयोग करें</t>
     </r>
     <r>
       <rPr>
@@ -598,7 +612,7 @@
         <color indexed="64"/>
         <rFont val="Droid Sans Devanagari"/>
       </rPr>
-      <t xml:space="preserve">और देश कोड शामिल है। उदाहरण के लिए</t>
+      <t>और देश कोड शामिल है। उदाहरण के लिए</t>
     </r>
     <r>
       <rPr>
@@ -606,35 +620,35 @@
         <color indexed="64"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">: +914712345678</t>
+      <t>: +914712345678</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Veuillez entrer un numéro local valide ou utiliser le format international standard, qui comprend un signe plus (+) et le code du pays. Par exemple: +254712345678</t>
+    <t>Veuillez entrer un numéro local valide ou utiliser le format international standard, qui comprend un signe plus (+) et le code du pays. Par exemple: +254712345678</t>
   </si>
   <si>
     <t>phone_alternate</t>
   </si>
   <si>
-    <t xml:space="preserve">Alternate Phone Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">अन्य फोन नंबर</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nomor Telepon Alternatif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nambari nyingine ya simu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">अन्य फोन नम्बर</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Téléphone alternatif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">select_one roles</t>
+    <t>Alternate Phone Number</t>
+  </si>
+  <si>
+    <t>अन्य फोन नंबर</t>
+  </si>
+  <si>
+    <t>Nomor Telepon Alternatif</t>
+  </si>
+  <si>
+    <t>nambari nyingine ya simu</t>
+  </si>
+  <si>
+    <t>अन्य फोन नम्बर</t>
+  </si>
+  <si>
+    <t>Téléphone alternatif</t>
+  </si>
+  <si>
+    <t>select_one roles</t>
   </si>
   <si>
     <t>role</t>
@@ -655,52 +669,52 @@
     <t>Rôle</t>
   </si>
   <si>
-    <t xml:space="preserve">Select the role that best suits this person</t>
-  </si>
-  <si>
-    <t xml:space="preserve">उस भूमिका का चयन करें जो इस व्यक्ति को सबसे अच्छा सूट करता है</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pilih peran yang paling cocok untuk orang ini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chagua jukumu linachoambatana na huyu mtu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">यस व्यक्तिका लागि उपयुक्त भूमिका छान्नुहोस्</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sélectionnez le rôle qui convient le mieux à cette personne</t>
+    <t>Select the role that best suits this person</t>
+  </si>
+  <si>
+    <t>उस भूमिका का चयन करें जो इस व्यक्ति को सबसे अच्छा सूट करता है</t>
+  </si>
+  <si>
+    <t>Pilih peran yang paling cocok untuk orang ini</t>
+  </si>
+  <si>
+    <t>Chagua jukumu linachoambatana na huyu mtu</t>
+  </si>
+  <si>
+    <t>यस व्यक्तिका लागि उपयुक्त भूमिका छान्नुहोस्</t>
+  </si>
+  <si>
+    <t>Sélectionnez le rôle qui convient le mieux à cette personne</t>
   </si>
   <si>
     <t>role_other</t>
   </si>
   <si>
-    <t xml:space="preserve">Specify other</t>
-  </si>
-  <si>
-    <t xml:space="preserve">अन्य का उल्‍लेख करें</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tentukan lainnya</t>
+    <t>Specify other</t>
+  </si>
+  <si>
+    <t>अन्य का उल्‍लेख करें</t>
+  </si>
+  <si>
+    <t>Tentukan lainnya</t>
   </si>
   <si>
     <t xml:space="preserve"> Jukumu lingine lelote</t>
   </si>
   <si>
-    <t xml:space="preserve">अन्य उल्लेख गर्नुहोस्</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autre rôle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">selected( ${role},'other')</t>
+    <t>अन्य उल्लेख गर्नुहोस्</t>
+  </si>
+  <si>
+    <t>Autre rôle</t>
+  </si>
+  <si>
+    <t>selected( ${role},'other')</t>
   </si>
   <si>
     <t>external_id</t>
   </si>
   <si>
-    <t xml:space="preserve">External ID</t>
+    <t>External ID</t>
   </si>
   <si>
     <r>
@@ -721,10 +735,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Eksternal ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID ya nje</t>
+    <t>Eksternal ID</t>
+  </si>
+  <si>
+    <t>ID ya nje</t>
   </si>
   <si>
     <r>
@@ -745,7 +759,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Identifiant externe</t>
+    <t>Identifiant externe</t>
   </si>
   <si>
     <t>notes</t>
@@ -775,7 +789,7 @@
     <t>create</t>
   </si>
   <si>
-    <t xml:space="preserve">${phone} != '' and (selected( ${role},'chw') or selected( ${role},'chw_supervisor'))</t>
+    <t>${phone} != '' and (selected( ${role},'chw') or selected( ${role},'chw_supervisor'))</t>
   </si>
   <si>
     <t>meta</t>
@@ -934,22 +948,22 @@
     <t>approx</t>
   </si>
   <si>
-    <t xml:space="preserve">Date of birth unknown</t>
+    <t>Date of birth unknown</t>
   </si>
   <si>
     <t xml:space="preserve">जन्म की तारीख का पता नहीं </t>
   </si>
   <si>
-    <t xml:space="preserve">Tanggal tidak diketahui lahir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tarehe ya Kuzaliwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">जन्म मिती थाहा नभएको</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date de naissance inconnue</t>
+    <t>Tanggal tidak diketahui lahir</t>
+  </si>
+  <si>
+    <t>Tarehe ya Kuzaliwa</t>
+  </si>
+  <si>
+    <t>जन्म मिती थाहा नभएको</t>
+  </si>
+  <si>
+    <t>Date de naissance inconnue</t>
   </si>
   <si>
     <t>roles</t>
@@ -961,16 +975,16 @@
     <t>CHW</t>
   </si>
   <si>
-    <t xml:space="preserve">सामुदायिक स्वास्थ्यकर्मी</t>
+    <t>सामुदायिक स्वास्थ्यकर्मी</t>
   </si>
   <si>
     <t>Kader</t>
   </si>
   <si>
-    <t xml:space="preserve">Mhudumu wa afya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">महिला स्वास्थ्य स्वयम् सेविका</t>
+    <t>Mhudumu wa afya</t>
+  </si>
+  <si>
+    <t>महिला स्वास्थ्य स्वयम् सेविका</t>
   </si>
   <si>
     <t>ASC</t>
@@ -979,22 +993,22 @@
     <t>chw_supervisor</t>
   </si>
   <si>
-    <t xml:space="preserve">CHW Supervisor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">सामुदायिक स्वास्थ्यकर्मी के मैनेजर</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kader Pengawas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mkuu wa wahudumu wa afya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">महिला स्वास्थ्य स्वयम् सेविकाको सुपरभाइजर</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Superviseur ASC</t>
+    <t>CHW Supervisor</t>
+  </si>
+  <si>
+    <t>सामुदायिक स्वास्थ्यकर्मी के मैनेजर</t>
+  </si>
+  <si>
+    <t>Kader Pengawas</t>
+  </si>
+  <si>
+    <t>Mkuu wa wahudumu wa afya</t>
+  </si>
+  <si>
+    <t>महिला स्वास्थ्य स्वयम् सेविकाको सुपरभाइजर</t>
+  </si>
+  <si>
+    <t>Superviseur ASC</t>
   </si>
   <si>
     <t>nurse</t>
@@ -1018,22 +1032,22 @@
     <t>manager</t>
   </si>
   <si>
-    <t xml:space="preserve">Facility Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">स्वास्थ्य केंद्र के मैनजर</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manajer Fasilitas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meneja wa Kituo cha afya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">स्वास्थ्य संस्था प्रमुख</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personnel médical</t>
+    <t>Facility Manager</t>
+  </si>
+  <si>
+    <t>स्वास्थ्य केंद्र के मैनजर</t>
+  </si>
+  <si>
+    <t>Manajer Fasilitas</t>
+  </si>
+  <si>
+    <t>Meneja wa Kituo cha afya</t>
+  </si>
+  <si>
+    <t>स्वास्थ्य संस्था प्रमुख</t>
+  </si>
+  <si>
+    <t>Personnel médical</t>
   </si>
   <si>
     <t>patient</t>
@@ -1078,7 +1092,7 @@
     <t>district_hospital</t>
   </si>
   <si>
-    <t xml:space="preserve">Health Facility</t>
+    <t>Health Facility</t>
   </si>
   <si>
     <t>ज़िला</t>
@@ -1093,7 +1107,7 @@
     <t>जिल्ला</t>
   </si>
   <si>
-    <t xml:space="preserve">Hôpital de District</t>
+    <t>Hôpital de District</t>
   </si>
   <si>
     <t>health_center</t>
@@ -1102,19 +1116,19 @@
     <t>Area</t>
   </si>
   <si>
-    <t xml:space="preserve">स्वास्थ्य केंद्र</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fasilitas Kesehatan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kituo cha afya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">स्वास्थ्य केन्द्र</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Centre de center</t>
+    <t>स्वास्थ्य केंद्र</t>
+  </si>
+  <si>
+    <t>Fasilitas Kesehatan</t>
+  </si>
+  <si>
+    <t>Kituo cha afya</t>
+  </si>
+  <si>
+    <t>स्वास्थ्य केन्द्र</t>
+  </si>
+  <si>
+    <t>Centre de center</t>
   </si>
   <si>
     <t>clinic</t>
@@ -1153,7 +1167,7 @@
     <t>default_language</t>
   </si>
   <si>
-    <t xml:space="preserve">New Person</t>
+    <t>New Person</t>
   </si>
   <si>
     <t>contact:person:create</t>
@@ -1163,38 +1177,37 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>select-contact</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color indexed="64"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10.000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color indexed="64"/>
       <name val="Droid Sans Devanagari"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1275,152 +1288,72 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="43" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="41" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="39">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
-      <protection hidden="0" locked="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
-      <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="2" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
-      <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="2" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf fontId="2" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf fontId="2" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf fontId="2" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="2" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="9" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="10" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="3" fillId="10" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="10" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="11" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="4" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="5" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="5" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="0">
-      <alignment wrapText="1"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="0">
-      <alignment wrapText="1"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="0">
-      <alignment wrapText="1"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="3" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="3" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="4" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyProtection="0">
-      <alignment wrapText="1"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="4" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1428,295 +1361,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <a:themeElements>
     <a:clrScheme name="">
       <a:dk1>
@@ -1768,7 +1421,7 @@
         <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1883,43 +1536,44 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr filterMode="0">
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr defaultColWidth="14.328125" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AR50"/>
+  <sheetFormatPr defaultColWidth="14.33203125" defaultRowHeight="14.4"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="0" width="21.43"/>
-    <col customWidth="1" min="2" max="2" style="0" width="22.43"/>
-    <col customWidth="1" min="3" max="3" style="0" width="44.710000000000001"/>
-    <col customWidth="1" min="4" max="4" style="0" width="27.300000000000001"/>
-    <col customWidth="1" min="5" max="5" style="0" width="29.140000000000001"/>
-    <col customWidth="1" min="6" max="6" style="0" width="16.57"/>
-    <col customWidth="1" min="7" max="7" style="0" width="33.859999999999999"/>
-    <col customWidth="1" min="8" max="8" style="0" width="12.859999999999999"/>
-    <col customWidth="1" min="9" max="9" style="0" width="13.710000000000001"/>
-    <col customWidth="1" min="10" max="10" style="0" width="8.6999999999999993"/>
-    <col customWidth="1" min="11" max="11" style="0" width="14.279999999999999"/>
-    <col customWidth="1" min="12" max="13" style="0" width="10.710000000000001"/>
-    <col customWidth="1" min="14" max="14" style="0" width="8.6999999999999993"/>
-    <col customWidth="1" min="15" max="16" style="0" width="18.140000000000001"/>
-    <col customWidth="1" min="17" max="17" style="0" width="23.300000000000001"/>
-    <col customWidth="1" min="18" max="20" style="0" width="18.140000000000001"/>
-    <col customWidth="1" min="21" max="21" style="0" width="22.57"/>
-    <col customWidth="1" min="22" max="22" style="0" width="36.700000000000003"/>
-    <col customWidth="1" min="23" max="23" style="0" width="8.6999999999999993"/>
-    <col customWidth="1" min="24" max="24" style="0" width="34.859999999999999"/>
-    <col customWidth="1" min="25" max="25" style="0" width="19.859999999999999"/>
-    <col customWidth="1" min="26" max="26" style="0" width="13.859999999999999"/>
-    <col customWidth="1" min="27" max="44" style="0" width="8.6999999999999993"/>
+    <col min="1" max="1" width="21.44140625" customWidth="1"/>
+    <col min="2" max="2" width="22.44140625" customWidth="1"/>
+    <col min="3" max="3" width="44.6640625" customWidth="1"/>
+    <col min="4" max="4" width="27.33203125" customWidth="1"/>
+    <col min="5" max="5" width="29.109375" customWidth="1"/>
+    <col min="6" max="6" width="16.5546875" customWidth="1"/>
+    <col min="7" max="7" width="33.88671875" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.21875" customWidth="1"/>
+    <col min="12" max="12" width="12.21875" customWidth="1"/>
+    <col min="13" max="13" width="10.6640625" customWidth="1"/>
+    <col min="14" max="14" width="8.6640625" customWidth="1"/>
+    <col min="15" max="16" width="18.109375" customWidth="1"/>
+    <col min="17" max="17" width="23.33203125" customWidth="1"/>
+    <col min="18" max="20" width="18.109375" customWidth="1"/>
+    <col min="21" max="21" width="22.5546875" customWidth="1"/>
+    <col min="22" max="22" width="36.6640625" customWidth="1"/>
+    <col min="23" max="23" width="8.6640625" customWidth="1"/>
+    <col min="24" max="24" width="34.88671875" customWidth="1"/>
+    <col min="25" max="25" width="19.88671875" customWidth="1"/>
+    <col min="26" max="26" width="13.88671875" customWidth="1"/>
+    <col min="27" max="32" width="8.6640625" customWidth="1"/>
+    <col min="33" max="33" width="15.77734375" customWidth="1"/>
+    <col min="34" max="44" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
+    <row r="1" spans="1:44" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2014,7 +1668,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="2" spans="1:44" ht="14.25" customHeight="1">
       <c r="A2" s="11" t="s">
         <v>31</v>
       </c>
@@ -2078,7 +1732,7 @@
       <c r="AQ2" s="12"/>
       <c r="AR2" s="12"/>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
+    <row r="3" spans="1:44" ht="14.25" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>31</v>
       </c>
@@ -2140,7 +1794,7 @@
       <c r="AQ3" s="12"/>
       <c r="AR3" s="12"/>
     </row>
-    <row r="4" ht="14.25" customHeight="1">
+    <row r="4" spans="1:44" ht="14.25" customHeight="1">
       <c r="A4" s="11" t="s">
         <v>36</v>
       </c>
@@ -2202,7 +1856,7 @@
       <c r="AQ4" s="12"/>
       <c r="AR4" s="12"/>
     </row>
-    <row r="5" ht="14.25" customHeight="1">
+    <row r="5" spans="1:44" ht="14.25" customHeight="1">
       <c r="A5" s="11" t="s">
         <v>36</v>
       </c>
@@ -2264,7 +1918,7 @@
       <c r="AQ5" s="12"/>
       <c r="AR5" s="12"/>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
+    <row r="6" spans="1:44" ht="14.25" customHeight="1">
       <c r="A6" s="11" t="s">
         <v>36</v>
       </c>
@@ -2326,7 +1980,7 @@
       <c r="AQ6" s="12"/>
       <c r="AR6" s="12"/>
     </row>
-    <row r="7" ht="14.25" customHeight="1">
+    <row r="7" spans="1:44" ht="14.25" customHeight="1">
       <c r="A7" s="11" t="s">
         <v>55</v>
       </c>
@@ -2374,7 +2028,7 @@
       <c r="AQ7" s="12"/>
       <c r="AR7" s="12"/>
     </row>
-    <row r="8" ht="14.25" customHeight="1">
+    <row r="8" spans="1:44" ht="14.25" customHeight="1">
       <c r="A8" s="11" t="s">
         <v>55</v>
       </c>
@@ -2422,7 +2076,7 @@
       <c r="AQ8" s="12"/>
       <c r="AR8" s="12"/>
     </row>
-    <row r="9" ht="14.25" customHeight="1">
+    <row r="9" spans="1:44" ht="14.25" customHeight="1">
       <c r="A9" s="11" t="s">
         <v>31</v>
       </c>
@@ -2486,7 +2140,7 @@
       <c r="AQ9" s="12"/>
       <c r="AR9" s="12"/>
     </row>
-    <row r="10" ht="14.25" customHeight="1">
+    <row r="10" spans="1:44" ht="14.25" customHeight="1">
       <c r="A10" s="11" t="s">
         <v>36</v>
       </c>
@@ -2515,10 +2169,10 @@
       <c r="J10" s="12"/>
       <c r="K10" s="12"/>
       <c r="L10" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="M10" s="12" t="s">
         <v>65</v>
-      </c>
-      <c r="M10" s="12" t="s">
-        <v>66</v>
       </c>
       <c r="N10" s="12"/>
       <c r="O10" s="12"/>
@@ -2529,27 +2183,27 @@
       <c r="T10" s="12"/>
       <c r="U10" s="12"/>
       <c r="V10" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="W10" s="12"/>
       <c r="X10" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y10" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Z10" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AA10" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AB10" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AC10" s="12"/>
       <c r="AD10" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AE10" s="12"/>
       <c r="AF10" s="12"/>
@@ -2566,7 +2220,7 @@
       <c r="AQ10" s="12"/>
       <c r="AR10" s="12"/>
     </row>
-    <row r="11" ht="14.25" customHeight="1">
+    <row r="11" spans="1:44" ht="14.25" customHeight="1">
       <c r="A11" s="11" t="s">
         <v>36</v>
       </c>
@@ -2595,7 +2249,7 @@
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
       <c r="L11" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M11" s="12"/>
       <c r="N11" s="12"/>
@@ -2630,7 +2284,7 @@
       <c r="AQ11" s="12"/>
       <c r="AR11" s="12"/>
     </row>
-    <row r="12" ht="14.25" customHeight="1">
+    <row r="12" spans="1:44" ht="14.25" customHeight="1">
       <c r="A12" s="11" t="s">
         <v>36</v>
       </c>
@@ -2659,7 +2313,7 @@
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
       <c r="L12" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M12" s="12"/>
       <c r="N12" s="12"/>
@@ -2694,12 +2348,12 @@
       <c r="AQ12" s="12"/>
       <c r="AR12" s="12"/>
     </row>
-    <row r="13" ht="14.25" customHeight="1">
+    <row r="13" spans="1:44" ht="14.25" customHeight="1">
       <c r="A13" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>70</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>71</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>33</v>
@@ -2723,7 +2377,7 @@
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
       <c r="L13" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M13" s="12"/>
       <c r="N13" s="12"/>
@@ -2735,7 +2389,7 @@
       <c r="T13" s="12"/>
       <c r="U13" s="12"/>
       <c r="V13" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="W13" s="12"/>
       <c r="X13" s="12"/>
@@ -2760,12 +2414,12 @@
       <c r="AQ13" s="12"/>
       <c r="AR13" s="12"/>
     </row>
-    <row r="14" ht="14.25" customHeight="1">
+    <row r="14" spans="1:44" ht="14.25" customHeight="1">
       <c r="A14" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>73</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>74</v>
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
@@ -2787,7 +2441,7 @@
       <c r="T14" s="12"/>
       <c r="U14" s="12"/>
       <c r="V14" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="W14" s="12"/>
       <c r="X14" s="12"/>
@@ -2812,7 +2466,7 @@
       <c r="AQ14" s="12"/>
       <c r="AR14" s="12"/>
     </row>
-    <row r="15" ht="14.25" customHeight="1">
+    <row r="15" spans="1:44" ht="14.25" customHeight="1">
       <c r="A15" s="11" t="s">
         <v>55</v>
       </c>
@@ -2860,7 +2514,7 @@
       <c r="AQ15" s="12"/>
       <c r="AR15" s="12"/>
     </row>
-    <row r="16" ht="14.25" customHeight="1">
+    <row r="16" spans="1:44" ht="14.25" customHeight="1">
       <c r="D16" s="15"/>
       <c r="E16" s="16"/>
       <c r="F16" s="17"/>
@@ -2881,12 +2535,12 @@
       <c r="AC16" s="19"/>
       <c r="AD16" s="20"/>
     </row>
-    <row r="17" ht="14.25" customHeight="1">
+    <row r="17" spans="1:44" ht="14.25" customHeight="1">
       <c r="A17" s="22" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C17" s="20" t="s">
         <v>33</v>
@@ -2943,29 +2597,29 @@
       <c r="AQ17" s="20"/>
       <c r="AR17" s="20"/>
     </row>
-    <row r="18" ht="14.25" customHeight="1">
+    <row r="18" spans="1:44" ht="14.25" customHeight="1">
       <c r="A18" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B18" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="D18" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="23" t="s">
+      <c r="E18" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="F18" s="20" t="s">
         <v>80</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>81</v>
       </c>
       <c r="G18" s="20"/>
       <c r="H18" s="20"/>
       <c r="I18" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J18" s="20"/>
       <c r="K18" s="20"/>
@@ -2989,7 +2643,7 @@
       <c r="AC18" s="20"/>
       <c r="AD18" s="20"/>
       <c r="AE18" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF18" s="20"/>
       <c r="AG18" s="20"/>
@@ -3005,29 +2659,29 @@
       <c r="AQ18" s="20"/>
       <c r="AR18" s="20"/>
     </row>
-    <row r="19" ht="14.25" customHeight="1">
+    <row r="19" spans="1:44" ht="14.25" customHeight="1">
       <c r="A19" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B19" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C19" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="23" t="s">
+      <c r="E19" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="E19" s="20" t="s">
+      <c r="F19" s="20" t="s">
         <v>86</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>87</v>
       </c>
       <c r="G19" s="20"/>
       <c r="H19" s="20"/>
       <c r="I19" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J19" s="20"/>
       <c r="K19" s="20"/>
@@ -3051,7 +2705,7 @@
       <c r="AC19" s="20"/>
       <c r="AD19" s="20"/>
       <c r="AE19" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AF19" s="20"/>
       <c r="AG19" s="20"/>
@@ -3067,7 +2721,7 @@
       <c r="AQ19" s="20"/>
       <c r="AR19" s="20"/>
     </row>
-    <row r="20" ht="14.25" customHeight="1">
+    <row r="20" spans="1:44" ht="14.25" customHeight="1">
       <c r="A20" s="22" t="s">
         <v>36</v>
       </c>
@@ -3075,26 +2729,26 @@
         <v>1</v>
       </c>
       <c r="C20" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="E20" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="F20" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="F20" s="20" t="s">
-        <v>92</v>
-      </c>
       <c r="G20" s="23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H20" s="20"/>
       <c r="I20" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J20" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K20" s="20"/>
       <c r="L20" s="20"/>
@@ -3131,15 +2785,15 @@
       <c r="AQ20" s="20"/>
       <c r="AR20" s="20"/>
     </row>
-    <row r="21" ht="14.25" customHeight="1">
+    <row r="21" spans="1:44" ht="14.25" customHeight="1">
       <c r="A21" s="22" t="s">
         <v>36</v>
       </c>
       <c r="B21" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="20" t="s">
         <v>94</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>95</v>
       </c>
       <c r="D21" s="20"/>
       <c r="E21" s="20"/>
@@ -3148,16 +2802,16 @@
       <c r="H21" s="20"/>
       <c r="I21" s="20"/>
       <c r="J21" s="20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K21" s="20"/>
       <c r="L21" s="20"/>
       <c r="M21" s="20"/>
       <c r="N21" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="O21" s="20" t="s">
         <v>97</v>
-      </c>
-      <c r="O21" s="20" t="s">
-        <v>98</v>
       </c>
       <c r="P21" s="20"/>
       <c r="Q21" s="20"/>
@@ -3168,7 +2822,7 @@
       <c r="V21" s="20"/>
       <c r="W21" s="20"/>
       <c r="X21" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Y21" s="20"/>
       <c r="Z21" s="20"/>
@@ -3191,12 +2845,12 @@
       <c r="AQ21" s="20"/>
       <c r="AR21" s="20"/>
     </row>
-    <row r="22" ht="14.25" customHeight="1">
+    <row r="22" spans="1:44" ht="14.25" customHeight="1">
       <c r="A22" s="22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
@@ -3206,7 +2860,7 @@
       <c r="H22" s="20"/>
       <c r="I22" s="25"/>
       <c r="J22" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K22" s="20"/>
       <c r="L22" s="20"/>
@@ -3220,7 +2874,7 @@
       <c r="T22" s="20"/>
       <c r="U22" s="20"/>
       <c r="V22" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="W22" s="20"/>
       <c r="X22" s="20"/>
@@ -3245,12 +2899,12 @@
       <c r="AQ22" s="20"/>
       <c r="AR22" s="20"/>
     </row>
-    <row r="23" ht="14.25" customHeight="1">
+    <row r="23" spans="1:44" ht="14.25" customHeight="1">
       <c r="A23" s="22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C23" s="25"/>
       <c r="D23" s="20"/>
@@ -3272,7 +2926,7 @@
       <c r="T23" s="20"/>
       <c r="U23" s="20"/>
       <c r="V23" s="20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="W23" s="20"/>
       <c r="X23" s="20"/>
@@ -3297,12 +2951,12 @@
       <c r="AQ23" s="20"/>
       <c r="AR23" s="20"/>
     </row>
-    <row r="24" ht="14.25" customHeight="1">
+    <row r="24" spans="1:44" ht="14.25" customHeight="1">
       <c r="A24" s="22" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C24" s="20" t="s">
         <v>33</v>
@@ -3349,15 +3003,15 @@
       <c r="AQ24" s="20"/>
       <c r="AR24" s="20"/>
     </row>
-    <row r="25" ht="14.25" customHeight="1">
+    <row r="25" spans="1:44" ht="14.25" customHeight="1">
       <c r="A25" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="B25" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="C25" s="20" t="s">
         <v>106</v>
-      </c>
-      <c r="C25" s="20" t="s">
-        <v>107</v>
       </c>
       <c r="D25" s="20"/>
       <c r="E25" s="20"/>
@@ -3366,18 +3020,18 @@
       <c r="H25" s="20"/>
       <c r="I25" s="20"/>
       <c r="J25" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K25" s="20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L25" s="20"/>
       <c r="M25" s="20"/>
       <c r="N25" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="O25" s="20" t="s">
         <v>109</v>
-      </c>
-      <c r="O25" s="20" t="s">
-        <v>110</v>
       </c>
       <c r="P25" s="20"/>
       <c r="Q25" s="20"/>
@@ -3388,7 +3042,7 @@
       <c r="V25" s="20"/>
       <c r="W25" s="20"/>
       <c r="X25" s="20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Y25" s="20"/>
       <c r="Z25" s="20"/>
@@ -3411,15 +3065,15 @@
       <c r="AQ25" s="20"/>
       <c r="AR25" s="20"/>
     </row>
-    <row r="26" ht="14.25" customHeight="1">
+    <row r="26" spans="1:44" ht="14.25" customHeight="1">
       <c r="A26" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="C26" s="20" t="s">
         <v>113</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>114</v>
       </c>
       <c r="D26" s="20"/>
       <c r="E26" s="20"/>
@@ -3429,7 +3083,7 @@
       <c r="I26" s="20"/>
       <c r="J26" s="20"/>
       <c r="K26" s="20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L26" s="20"/>
       <c r="M26" s="20"/>
@@ -3465,15 +3119,15 @@
       <c r="AQ26" s="20"/>
       <c r="AR26" s="20"/>
     </row>
-    <row r="27" ht="14.25" customHeight="1">
+    <row r="27" spans="1:44" ht="14.25" customHeight="1">
       <c r="A27" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="C27" s="20" t="s">
         <v>117</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>118</v>
       </c>
       <c r="D27" s="20"/>
       <c r="E27" s="20"/>
@@ -3482,18 +3136,18 @@
       <c r="H27" s="20"/>
       <c r="I27" s="20"/>
       <c r="J27" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K27" s="20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L27" s="20"/>
       <c r="M27" s="20"/>
       <c r="N27" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="O27" s="20" t="s">
         <v>119</v>
-      </c>
-      <c r="O27" s="20" t="s">
-        <v>120</v>
       </c>
       <c r="P27" s="20"/>
       <c r="Q27" s="20"/>
@@ -3525,15 +3179,15 @@
       <c r="AQ27" s="20"/>
       <c r="AR27" s="20"/>
     </row>
-    <row r="28" ht="14.25" customHeight="1">
+    <row r="28" spans="1:44" ht="14.25" customHeight="1">
       <c r="A28" s="22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B28" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" s="20" t="s">
         <v>121</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>122</v>
       </c>
       <c r="D28" s="20"/>
       <c r="E28" s="20"/>
@@ -3543,15 +3197,15 @@
       <c r="I28" s="20"/>
       <c r="J28" s="20"/>
       <c r="K28" s="20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L28" s="20"/>
       <c r="M28" s="20"/>
       <c r="N28" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="O28" s="20" t="s">
         <v>123</v>
-      </c>
-      <c r="O28" s="20" t="s">
-        <v>124</v>
       </c>
       <c r="P28" s="20"/>
       <c r="Q28" s="20"/>
@@ -3583,15 +3237,15 @@
       <c r="AQ28" s="20"/>
       <c r="AR28" s="20"/>
     </row>
-    <row r="29" ht="14.25" customHeight="1">
+    <row r="29" spans="1:44" ht="14.25" customHeight="1">
       <c r="A29" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="C29" s="20" t="s">
         <v>126</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>127</v>
       </c>
       <c r="D29" s="20"/>
       <c r="E29" s="20"/>
@@ -3602,7 +3256,7 @@
       <c r="J29" s="20"/>
       <c r="K29" s="20"/>
       <c r="L29" s="20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M29" s="20"/>
       <c r="N29" s="20"/>
@@ -3637,12 +3291,12 @@
       <c r="AQ29" s="20"/>
       <c r="AR29" s="20"/>
     </row>
-    <row r="30" ht="14.25" customHeight="1">
+    <row r="30" spans="1:44" ht="14.25" customHeight="1">
       <c r="A30" s="22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C30" s="25"/>
       <c r="D30" s="20"/>
@@ -3664,7 +3318,7 @@
       <c r="T30" s="20"/>
       <c r="U30" s="20"/>
       <c r="V30" s="25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="W30" s="20"/>
       <c r="X30" s="20"/>
@@ -3689,12 +3343,12 @@
       <c r="AQ30" s="20"/>
       <c r="AR30" s="20"/>
     </row>
-    <row r="31" ht="14.25" customHeight="1">
+    <row r="31" spans="1:44" ht="14.25" customHeight="1">
       <c r="A31" s="22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="20"/>
@@ -3716,7 +3370,7 @@
       <c r="T31" s="25"/>
       <c r="U31" s="20"/>
       <c r="V31" s="26" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="W31" s="20"/>
       <c r="X31" s="20"/>
@@ -3741,12 +3395,12 @@
       <c r="AQ31" s="20"/>
       <c r="AR31" s="20"/>
     </row>
-    <row r="32" ht="14.25" customHeight="1">
+    <row r="32" spans="1:44" ht="14.25" customHeight="1">
       <c r="A32" s="22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C32" s="25"/>
       <c r="D32" s="20"/>
@@ -3768,7 +3422,7 @@
       <c r="T32" s="20"/>
       <c r="U32" s="20"/>
       <c r="V32" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="W32" s="20"/>
       <c r="X32" s="20"/>
@@ -3793,15 +3447,15 @@
       <c r="AQ32" s="20"/>
       <c r="AR32" s="20"/>
     </row>
-    <row r="33" ht="14.25" customHeight="1">
+    <row r="33" spans="1:44" ht="14.25" customHeight="1">
       <c r="A33" s="22" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B33" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="C33" s="27" t="s">
         <v>135</v>
-      </c>
-      <c r="C33" s="27" t="s">
-        <v>136</v>
       </c>
       <c r="D33" s="20"/>
       <c r="E33" s="20"/>
@@ -3847,7 +3501,7 @@
       <c r="AQ33" s="20"/>
       <c r="AR33" s="20"/>
     </row>
-    <row r="34" ht="14.25" customHeight="1">
+    <row r="34" spans="1:44" ht="14.25" customHeight="1">
       <c r="A34" s="22" t="s">
         <v>55</v>
       </c>
@@ -3895,38 +3549,38 @@
       <c r="AQ34" s="20"/>
       <c r="AR34" s="20"/>
     </row>
-    <row r="35" ht="14.25" customHeight="1">
+    <row r="35" spans="1:44" ht="14.25" customHeight="1">
       <c r="A35" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="B35" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="C35" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="C35" s="20" t="s">
+      <c r="D35" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="D35" s="23" t="s">
+      <c r="E35" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="E35" s="20" t="s">
+      <c r="F35" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="F35" s="20" t="s">
-        <v>142</v>
-      </c>
       <c r="G35" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H35" s="20"/>
       <c r="I35" s="20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J35" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K35" s="20"/>
       <c r="L35" s="20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M35" s="20"/>
       <c r="N35" s="20"/>
@@ -3961,51 +3615,51 @@
       <c r="AQ35" s="20"/>
       <c r="AR35" s="20"/>
     </row>
-    <row r="36" ht="14.25" customHeight="1">
+    <row r="36" spans="1:44" ht="14.25" customHeight="1">
       <c r="A36" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="B36" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="B36" s="22" t="s">
+      <c r="C36" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="C36" s="20" t="s">
+      <c r="D36" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="D36" s="23" t="s">
+      <c r="E36" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="E36" s="20" t="s">
+      <c r="F36" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F36" s="20" t="s">
+      <c r="G36" s="23" t="s">
         <v>149</v>
-      </c>
-      <c r="G36" s="23" t="s">
-        <v>150</v>
       </c>
       <c r="H36" s="20"/>
       <c r="I36" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J36" s="20"/>
       <c r="K36" s="20"/>
       <c r="L36" s="20"/>
       <c r="M36" s="20"/>
       <c r="N36" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="O36" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="O36" s="20" t="s">
+      <c r="P36" s="28" t="s">
         <v>153</v>
-      </c>
-      <c r="P36" s="28" t="s">
-        <v>154</v>
       </c>
       <c r="Q36" s="20"/>
       <c r="R36" s="20"/>
       <c r="S36" s="20"/>
       <c r="T36" s="20"/>
       <c r="U36" s="20" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="V36" s="20"/>
       <c r="W36" s="20"/>
@@ -4031,51 +3685,51 @@
       <c r="AQ36" s="20"/>
       <c r="AR36" s="20"/>
     </row>
-    <row r="37" ht="14.25" customHeight="1">
+    <row r="37" spans="1:44" ht="14.25" customHeight="1">
       <c r="A37" s="22" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B37" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="C37" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="C37" s="20" t="s">
+      <c r="D37" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="D37" s="23" t="s">
+      <c r="E37" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="E37" s="20" t="s">
+      <c r="F37" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="F37" s="20" t="s">
+      <c r="G37" s="23" t="s">
         <v>160</v>
-      </c>
-      <c r="G37" s="23" t="s">
-        <v>161</v>
       </c>
       <c r="H37" s="20"/>
       <c r="I37" s="20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J37" s="20"/>
       <c r="K37" s="20"/>
       <c r="L37" s="20"/>
       <c r="M37" s="20"/>
       <c r="N37" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="O37" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="O37" s="20" t="s">
+      <c r="P37" s="28" t="s">
         <v>153</v>
-      </c>
-      <c r="P37" s="28" t="s">
-        <v>154</v>
       </c>
       <c r="Q37" s="20"/>
       <c r="R37" s="20"/>
       <c r="S37" s="20"/>
       <c r="T37" s="20"/>
       <c r="U37" s="20" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="V37" s="20"/>
       <c r="W37" s="20"/>
@@ -4101,31 +3755,31 @@
       <c r="AQ37" s="20"/>
       <c r="AR37" s="20"/>
     </row>
-    <row r="38" ht="14.25" customHeight="1">
+    <row r="38" spans="1:44" ht="14.25" customHeight="1">
       <c r="A38" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="B38" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="B38" s="22" t="s">
+      <c r="C38" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="C38" s="20" t="s">
+      <c r="D38" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="D38" s="23" t="s">
+      <c r="E38" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="E38" s="20" t="s">
+      <c r="F38" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="F38" s="20" t="s">
-        <v>168</v>
-      </c>
       <c r="G38" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H38" s="20"/>
       <c r="I38" s="20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J38" s="20"/>
       <c r="K38" s="20"/>
@@ -4142,23 +3796,23 @@
       <c r="V38" s="20"/>
       <c r="W38" s="20"/>
       <c r="X38" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y38" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="Y38" s="23" t="s">
+      <c r="Z38" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="Z38" s="20" t="s">
+      <c r="AA38" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="AA38" s="20" t="s">
+      <c r="AB38" s="23" t="s">
         <v>173</v>
-      </c>
-      <c r="AB38" s="23" t="s">
-        <v>174</v>
       </c>
       <c r="AC38" s="20"/>
       <c r="AD38" s="20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AE38" s="20"/>
       <c r="AF38" s="20"/>
@@ -4175,37 +3829,37 @@
       <c r="AQ38" s="20"/>
       <c r="AR38" s="20"/>
     </row>
-    <row r="39" ht="14.25" customHeight="1">
+    <row r="39" spans="1:44" ht="14.25" customHeight="1">
       <c r="A39" s="22" t="s">
         <v>36</v>
       </c>
       <c r="B39" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="C39" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="C39" s="20" t="s">
+      <c r="D39" s="23" t="s">
         <v>177</v>
       </c>
-      <c r="D39" s="23" t="s">
+      <c r="E39" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="E39" s="20" t="s">
+      <c r="F39" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="F39" s="20" t="s">
+      <c r="G39" s="23" t="s">
         <v>180</v>
-      </c>
-      <c r="G39" s="23" t="s">
-        <v>181</v>
       </c>
       <c r="H39" s="20"/>
       <c r="I39" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="J39" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="K39" s="20" t="s">
         <v>182</v>
-      </c>
-      <c r="J39" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="K39" s="20" t="s">
-        <v>183</v>
       </c>
       <c r="L39" s="20"/>
       <c r="M39" s="20"/>
@@ -4241,31 +3895,31 @@
       <c r="AQ39" s="20"/>
       <c r="AR39" s="20"/>
     </row>
-    <row r="40" ht="14.25" customHeight="1">
+    <row r="40" spans="1:44" ht="14.25" customHeight="1">
       <c r="A40" s="22" t="s">
         <v>36</v>
       </c>
       <c r="B40" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="C40" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="C40" s="20" t="s">
+      <c r="D40" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="D40" s="23" t="s">
+      <c r="E40" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="E40" s="20" t="s">
+      <c r="F40" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="F40" s="20" t="s">
+      <c r="G40" s="23" t="s">
         <v>188</v>
-      </c>
-      <c r="G40" s="23" t="s">
-        <v>189</v>
       </c>
       <c r="H40" s="20"/>
       <c r="I40" s="20" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J40" s="20"/>
       <c r="K40" s="20"/>
@@ -4303,36 +3957,36 @@
       <c r="AQ40" s="20"/>
       <c r="AR40" s="20"/>
     </row>
-    <row r="41" ht="14.25" customHeight="1">
+    <row r="41" spans="1:44" ht="14.25" customHeight="1">
       <c r="A41" s="22" t="s">
         <v>36</v>
       </c>
       <c r="B41" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="C41" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="C41" s="20" t="s">
+      <c r="D41" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="D41" s="23" t="s">
+      <c r="E41" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="E41" s="20" t="s">
+      <c r="F41" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="F41" s="20" t="s">
+      <c r="G41" s="23" t="s">
         <v>195</v>
-      </c>
-      <c r="G41" s="23" t="s">
-        <v>196</v>
       </c>
       <c r="H41" s="20"/>
       <c r="I41" s="20" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J41" s="20"/>
       <c r="K41" s="20"/>
       <c r="L41" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M41" s="20"/>
       <c r="N41" s="20"/>
@@ -4367,12 +4021,12 @@
       <c r="AQ41" s="20"/>
       <c r="AR41" s="20"/>
     </row>
-    <row r="42" ht="14.25" customHeight="1">
+    <row r="42" spans="1:44" ht="14.25" customHeight="1">
       <c r="A42" s="22" t="s">
         <v>31</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C42" s="20" t="s">
         <v>33</v>
@@ -4429,12 +4083,12 @@
       <c r="AQ42" s="20"/>
       <c r="AR42" s="20"/>
     </row>
-    <row r="43" ht="14.25" customHeight="1">
+    <row r="43" spans="1:44" ht="14.25" customHeight="1">
       <c r="A43" s="22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C43" s="20"/>
       <c r="D43" s="20"/>
@@ -4456,7 +4110,7 @@
       <c r="T43" s="20"/>
       <c r="U43" s="20"/>
       <c r="V43" s="29" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="W43" s="20"/>
       <c r="X43" s="20"/>
@@ -4481,7 +4135,7 @@
       <c r="AQ43" s="20"/>
       <c r="AR43" s="20"/>
     </row>
-    <row r="44" ht="14.25" customHeight="1">
+    <row r="44" spans="1:44" ht="14.25" customHeight="1">
       <c r="A44" s="22" t="s">
         <v>55</v>
       </c>
@@ -4529,12 +4183,12 @@
       <c r="AQ44" s="20"/>
       <c r="AR44" s="20"/>
     </row>
-    <row r="45" ht="14.25" customHeight="1">
+    <row r="45" spans="1:44" ht="14.25" customHeight="1">
       <c r="A45" s="22" t="s">
         <v>31</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C45" s="20" t="s">
         <v>33</v>
@@ -4558,7 +4212,7 @@
       <c r="J45" s="20"/>
       <c r="K45" s="20"/>
       <c r="L45" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M45" s="20"/>
       <c r="N45" s="20"/>
@@ -4593,12 +4247,12 @@
       <c r="AQ45" s="20"/>
       <c r="AR45" s="20"/>
     </row>
-    <row r="46" ht="14.25" customHeight="1">
+    <row r="46" spans="1:44" ht="14.25" customHeight="1">
       <c r="A46" s="22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C46" s="20"/>
       <c r="D46" s="20"/>
@@ -4620,7 +4274,7 @@
       <c r="T46" s="20"/>
       <c r="U46" s="20"/>
       <c r="V46" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="W46" s="20"/>
       <c r="X46" s="20"/>
@@ -4645,12 +4299,12 @@
       <c r="AQ46" s="20"/>
       <c r="AR46" s="20"/>
     </row>
-    <row r="47" ht="14.25" customHeight="1">
+    <row r="47" spans="1:44" ht="14.25" customHeight="1">
       <c r="A47" s="22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C47" s="20"/>
       <c r="D47" s="20"/>
@@ -4672,7 +4326,7 @@
       <c r="T47" s="20"/>
       <c r="U47" s="20"/>
       <c r="V47" s="20" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W47" s="20"/>
       <c r="X47" s="20"/>
@@ -4697,12 +4351,12 @@
       <c r="AQ47" s="20"/>
       <c r="AR47" s="20"/>
     </row>
-    <row r="48" ht="14.25" customHeight="1">
+    <row r="48" spans="1:44" ht="14.25" customHeight="1">
       <c r="A48" s="22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B48" s="22" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C48" s="20"/>
       <c r="D48" s="20"/>
@@ -4724,7 +4378,7 @@
       <c r="T48" s="20"/>
       <c r="U48" s="20"/>
       <c r="V48" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="W48" s="20"/>
       <c r="X48" s="20"/>
@@ -4749,7 +4403,7 @@
       <c r="AQ48" s="20"/>
       <c r="AR48" s="20"/>
     </row>
-    <row r="49" ht="14.25" customHeight="1">
+    <row r="49" spans="1:44" ht="14.25" customHeight="1">
       <c r="A49" s="22" t="s">
         <v>55</v>
       </c>
@@ -4797,7 +4451,7 @@
       <c r="AQ49" s="20"/>
       <c r="AR49" s="20"/>
     </row>
-    <row r="50" ht="14.25" customHeight="1">
+    <row r="50" spans="1:44" ht="14.25" customHeight="1">
       <c r="A50" s="22" t="s">
         <v>55</v>
       </c>
@@ -4845,40 +4499,33 @@
       <c r="AQ50" s="20"/>
       <c r="AR50" s="20"/>
     </row>
-    <row r="1048575" ht="12.800000000000001"/>
-    <row r="1048576" ht="12.800000000000001"/>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr filterMode="0">
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr defaultColWidth="14.328125" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultColWidth="14.33203125" defaultRowHeight="14.4"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="0" width="21.149999999999999"/>
-    <col customWidth="1" min="2" max="2" style="0" width="16.289999999999999"/>
-    <col customWidth="1" min="3" max="3" style="0" width="28.719999999999999"/>
-    <col customWidth="1" min="4" max="4" style="0" width="29.57"/>
-    <col customWidth="1" min="5" max="5" style="0" width="26.149999999999999"/>
-    <col customWidth="1" min="6" max="6" style="0" width="16.57"/>
-    <col customWidth="1" min="7" max="7" style="0" width="36.700000000000003"/>
-    <col customWidth="1" min="8" max="8" style="0" width="12.859999999999999"/>
-    <col customWidth="1" min="9" max="9" style="0" width="13.710000000000001"/>
-    <col customWidth="1" min="10" max="13" style="0" width="7.7000000000000002"/>
-    <col customWidth="1" min="14" max="26" style="0" width="15.140000000000001"/>
+    <col min="1" max="1" width="21.109375" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="28.6640625" customWidth="1"/>
+    <col min="4" max="4" width="29.5546875" customWidth="1"/>
+    <col min="5" max="5" width="26.109375" customWidth="1"/>
+    <col min="6" max="6" width="16.5546875" customWidth="1"/>
+    <col min="7" max="7" width="36.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" customWidth="1"/>
+    <col min="10" max="13" width="7.6640625" customWidth="1"/>
+    <col min="14" max="26" width="15.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
+    <row r="1" spans="1:9" ht="14.25" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B1" s="30" t="s">
         <v>1</v>
@@ -4905,512 +4552,507 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="2" spans="1:9" ht="14.25" customHeight="1">
       <c r="A2" s="31" t="s">
+        <v>208</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="31" t="s">
         <v>209</v>
       </c>
-      <c r="B2" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" s="31" t="s">
+      <c r="D2" s="32" t="s">
         <v>210</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="E2" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="F2" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="G2" s="33" t="s">
         <v>213</v>
-      </c>
-      <c r="G2" s="33" t="s">
-        <v>214</v>
       </c>
       <c r="H2" s="19"/>
       <c r="I2" s="20" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A3" s="31" t="s">
+        <v>208</v>
+      </c>
+      <c r="B3" s="31" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="B3" s="31" t="s">
+      <c r="C3" s="31" t="s">
         <v>216</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="D3" s="32" t="s">
         <v>217</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="E3" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="F3" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="G3" s="33" t="s">
         <v>220</v>
-      </c>
-      <c r="G3" s="33" t="s">
-        <v>221</v>
       </c>
       <c r="H3" s="19"/>
       <c r="I3" s="20" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A4" s="31" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="31" t="s">
+      <c r="B4" s="31" t="s">
         <v>223</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="C4" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="D4" s="34" t="s">
         <v>225</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="E4" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="F4" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="G4" s="33" t="s">
         <v>228</v>
-      </c>
-      <c r="G4" s="33" t="s">
-        <v>229</v>
       </c>
       <c r="H4" s="19"/>
       <c r="I4" s="20" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A5" s="31" t="s">
+        <v>222</v>
+      </c>
+      <c r="B5" s="31" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="B5" s="31" t="s">
+      <c r="C5" s="31" t="s">
         <v>231</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="D5" s="34" t="s">
         <v>232</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="E5" s="16" t="s">
         <v>233</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="F5" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="G5" s="33" t="s">
         <v>235</v>
-      </c>
-      <c r="G5" s="33" t="s">
-        <v>236</v>
       </c>
       <c r="H5" s="19"/>
       <c r="I5" s="20" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A6" s="31" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="31" t="s">
+      <c r="B6" s="31" t="s">
+        <v>223</v>
+      </c>
+      <c r="C6" s="31" t="s">
         <v>238</v>
       </c>
-      <c r="B6" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="C6" s="31" t="s">
+      <c r="D6" s="34" t="s">
         <v>239</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="E6" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="F6" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="G6" s="33" t="s">
         <v>242</v>
-      </c>
-      <c r="G6" s="33" t="s">
-        <v>243</v>
       </c>
       <c r="H6" s="19"/>
       <c r="I6" s="20" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A7" s="31" t="s">
+        <v>237</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="C7" s="31" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="31" t="s">
-        <v>238</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>231</v>
-      </c>
-      <c r="C7" s="31" t="s">
+      <c r="D7" s="34" t="s">
         <v>245</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="E7" s="16" t="s">
         <v>246</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="F7" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="G7" s="33" t="s">
         <v>248</v>
-      </c>
-      <c r="G7" s="33" t="s">
-        <v>249</v>
       </c>
       <c r="H7" s="19"/>
       <c r="I7" s="20" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A8" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" t="s">
+      <c r="B8" s="35" t="s">
         <v>251</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="C8" s="36" t="s">
         <v>252</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="D8" s="34" t="s">
         <v>253</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="E8" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="F8" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="G8" s="33" t="s">
         <v>256</v>
-      </c>
-      <c r="G8" s="33" t="s">
-        <v>257</v>
       </c>
       <c r="H8" s="19"/>
       <c r="I8" s="20" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A9" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" t="s">
+      <c r="B9" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="C9" s="36" t="s">
         <v>260</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="D9" s="34" t="s">
         <v>261</v>
       </c>
-      <c r="D9" s="34" t="s">
+      <c r="E9" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="F9" s="17" t="s">
         <v>263</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="G9" s="33" t="s">
         <v>264</v>
-      </c>
-      <c r="G9" s="33" t="s">
-        <v>265</v>
       </c>
       <c r="H9" s="19"/>
       <c r="I9" s="20" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A10" t="s">
+        <v>258</v>
+      </c>
+      <c r="B10" s="35" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" t="s">
-        <v>259</v>
-      </c>
-      <c r="B10" s="35" t="s">
+      <c r="C10" s="36" t="s">
         <v>267</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="D10" s="34" t="s">
         <v>268</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="E10" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="F10" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="G10" s="33" t="s">
         <v>271</v>
-      </c>
-      <c r="G10" s="33" t="s">
-        <v>272</v>
       </c>
       <c r="H10" s="19"/>
       <c r="I10" s="20" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A11" t="s">
+        <v>258</v>
+      </c>
+      <c r="B11" s="35" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" t="s">
-        <v>259</v>
-      </c>
-      <c r="B11" s="35" t="s">
+      <c r="C11" s="36" t="s">
         <v>274</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="D11" s="34" t="s">
         <v>275</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="E11" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="F11" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="F11" s="17" t="s">
-        <v>278</v>
-      </c>
       <c r="G11" s="33" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H11" s="19"/>
       <c r="I11" s="20" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A12" t="s">
+        <v>258</v>
+      </c>
+      <c r="B12" s="35" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" t="s">
-        <v>259</v>
-      </c>
-      <c r="B12" s="35" t="s">
+      <c r="C12" s="36" t="s">
         <v>280</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="D12" s="34" t="s">
         <v>281</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="E12" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="F12" s="17" t="s">
         <v>283</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="G12" s="37" t="s">
         <v>284</v>
-      </c>
-      <c r="G12" s="37" t="s">
-        <v>285</v>
       </c>
       <c r="H12" s="19"/>
       <c r="I12" s="20" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A13" t="s">
+        <v>258</v>
+      </c>
+      <c r="B13" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" t="s">
-        <v>259</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>287</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" s="32" t="s">
         <v>288</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="E13" s="16" t="s">
         <v>289</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="F13" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="F13" s="17" t="s">
+      <c r="G13" s="33" t="s">
         <v>291</v>
-      </c>
-      <c r="G13" s="33" t="s">
-        <v>292</v>
       </c>
       <c r="H13" s="19"/>
       <c r="I13" s="20" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="14.25" customHeight="1">
       <c r="A14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B14" s="35" t="s">
+        <v>292</v>
+      </c>
+      <c r="C14" s="36" t="s">
         <v>293</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="D14" s="32" t="s">
         <v>294</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="E14" s="16" t="s">
         <v>295</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="F14" s="17" t="s">
         <v>296</v>
       </c>
-      <c r="F14" s="17" t="s">
-        <v>297</v>
-      </c>
       <c r="G14" s="33" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H14" s="19"/>
       <c r="I14" s="20" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A15" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" t="s">
+      <c r="B15" s="35" t="s">
         <v>299</v>
       </c>
-      <c r="B15" s="35" t="s">
+      <c r="C15" s="36" t="s">
         <v>300</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="D15" s="32" t="s">
         <v>301</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="E15" s="16" t="s">
         <v>302</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="F15" s="17" t="s">
         <v>303</v>
       </c>
-      <c r="F15" s="17" t="s">
+      <c r="G15" s="33" t="s">
         <v>304</v>
-      </c>
-      <c r="G15" s="33" t="s">
-        <v>305</v>
       </c>
       <c r="H15" s="19"/>
       <c r="I15" s="20" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A16" t="s">
+        <v>298</v>
+      </c>
+      <c r="B16" s="35" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" t="s">
-        <v>299</v>
-      </c>
-      <c r="B16" s="35" t="s">
+      <c r="C16" s="36" t="s">
         <v>307</v>
       </c>
-      <c r="C16" s="36" t="s">
+      <c r="D16" s="32" t="s">
         <v>308</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="E16" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="F16" s="17" t="s">
         <v>310</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="G16" s="33" t="s">
         <v>311</v>
-      </c>
-      <c r="G16" s="33" t="s">
-        <v>312</v>
       </c>
       <c r="H16" s="19"/>
       <c r="I16" s="20" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A17" t="s">
+        <v>298</v>
+      </c>
+      <c r="B17" s="35" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" t="s">
-        <v>299</v>
-      </c>
-      <c r="B17" s="35" t="s">
+      <c r="C17" s="36" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="D17" s="32" t="s">
         <v>315</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="E17" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="F17" s="17" t="s">
         <v>317</v>
       </c>
-      <c r="F17" s="17" t="s">
-        <v>318</v>
-      </c>
       <c r="G17" s="33" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H17" s="19"/>
       <c r="I17" s="20" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr filterMode="0">
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr defaultColWidth="14.328125" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:F1000"/>
+  <sheetFormatPr defaultColWidth="14.33203125" defaultRowHeight="14.4"/>
   <cols>
-    <col customWidth="1" min="1" max="2" style="0" width="7.7000000000000002"/>
-    <col customWidth="1" min="3" max="3" style="0" width="20.43"/>
-    <col customWidth="1" min="4" max="15" style="0" width="7.7000000000000002"/>
-    <col customWidth="1" min="16" max="26" style="0" width="15.140000000000001"/>
+    <col min="1" max="2" width="7.6640625" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" customWidth="1"/>
+    <col min="4" max="15" width="7.6640625" customWidth="1"/>
+    <col min="16" max="26" width="15.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
+    <row r="1" spans="1:6" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A2" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>326</v>
-      </c>
-      <c r="B2" t="s">
-        <v>327</v>
       </c>
       <c r="C2" s="38" t="str">
         <f ca="1">TEXT(NOW(), "yyyy-mm-dd_HH-MM")</f>
-        <v xml:space="preserve">2023-02-14 7-40</v>
+        <v>2025-05-01 22-35</v>
       </c>
       <c r="E2" t="s">
+        <v>327</v>
+      </c>
+      <c r="F2" t="s">
         <v>328</v>
       </c>
-      <c r="F2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="3" ht="14.25" customHeight="1"/>
-    <row r="4" ht="14.25" customHeight="1"/>
-    <row r="5" ht="14.25" customHeight="1"/>
-    <row r="6" ht="14.25" customHeight="1"/>
-    <row r="7" ht="14.25" customHeight="1"/>
-    <row r="8" ht="14.25" customHeight="1"/>
-    <row r="9" ht="14.25" customHeight="1"/>
-    <row r="10" ht="14.25" customHeight="1"/>
-    <row r="11" ht="14.25" customHeight="1"/>
-    <row r="12" ht="14.25" customHeight="1"/>
-    <row r="13" ht="14.25" customHeight="1"/>
-    <row r="14" ht="14.25" customHeight="1"/>
-    <row r="15" ht="14.25" customHeight="1"/>
-    <row r="16" ht="14.25" customHeight="1"/>
+    </row>
+    <row r="3" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="4" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="5" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="6" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="7" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="8" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="9" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="10" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="11" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="12" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="13" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="14" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="15" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="16" spans="1:6" ht="14.25" customHeight="1"/>
     <row r="17" ht="14.25" customHeight="1"/>
     <row r="18" ht="14.25" customHeight="1"/>
     <row r="19" ht="14.25" customHeight="1"/>
@@ -6396,9 +6038,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>